--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1-ballot</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:14:00+00:00</t>
+    <t>2024-03-29T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:28:39+00:00</t>
+    <t>2024-04-02T09:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:17:05+00:00</t>
+    <t>2024-04-02T09:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:24:51+00:00</t>
+    <t>2024-04-02T09:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:46:01+00:00</t>
+    <t>2024-04-02T14:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:06:21+00:00</t>
+    <t>2024-04-02T14:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T09:39:19+00:00</t>
+    <t>2024-06-10T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T12:17:15+00:00</t>
+    <t>2024-06-11T12:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:10:45+00:00</t>
+    <t>2024-06-11T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:11:06+00:00</t>
+    <t>2024-06-14T08:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:12:27+00:00</t>
+    <t>2024-06-14T08:15:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:15:01+00:00</t>
+    <t>2024-06-19T07:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-19T07:50:19+00:00</t>
+    <t>2024-06-20T09:03:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -868,7 +868,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1659,10 +1659,6 @@
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
-</t>
   </si>
   <si>
     <t>Référence vers la ressource Patient titulaire du dossier.</t>
@@ -9725,13 +9721,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>274</v>
@@ -9817,15 +9813,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9848,16 +9844,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9907,7 +9903,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9925,22 +9921,22 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-20T09:03:18+00:00</t>
+    <t>2024-06-26T16:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T16:31:19+00:00</t>
+    <t>2024-07-24T15:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T15:57:10+00:00</t>
+    <t>2024-07-25T10:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T10:14:34+00:00</t>
+    <t>2024-07-31T08:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T08:54:42+00:00</t>
+    <t>2024-09-06T13:26:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -281,7 +281,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -337,17 +337,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DocumentReference.meta.id</t>
   </si>
   <si>
@@ -505,12 +498,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
     <t>DocumentReference.meta.tag</t>
   </si>
   <si>
@@ -625,6 +612,9 @@
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>DocumentReference.extension</t>
@@ -859,9 +849,6 @@
     <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>DocumentEntry.class</t>
   </si>
   <si>
@@ -878,13 +865,6 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1218,13 +1198,6 @@
   </si>
   <si>
     <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
-  </si>
-  <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
   </si>
   <si>
     <t>Composition.language, 
@@ -1254,9 +1227,6 @@
   </si>
   <si>
     <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Processors of the data need to be able to know how to interpret the data.</t>
@@ -1576,14 +1546,6 @@
     <t>The time period over which the service that is described by the document was provided.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Composition.event.period</t>
   </si>
   <si>
@@ -1597,9 +1559,6 @@
 @value</t>
   </si>
   <si>
-    <t>DR</t>
-  </si>
-  <si>
     <t>DocumentEntry.serviceStartTime, DocumentEntry.serviceStopTime</t>
   </si>
   <si>
@@ -1610,9 +1569,6 @@
   </si>
   <si>
     <t>The kind of facility where the patient was seen.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS</t>
@@ -2530,11 +2486,11 @@
         <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
       </c>
@@ -2542,7 +2498,7 @@
         <v>80</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>80</v>
@@ -2559,10 +2515,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2585,13 +2541,13 @@
         <v>80</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2642,7 +2598,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -2663,7 +2619,7 @@
         <v>80</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>80</v>
@@ -2680,14 +2636,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2706,16 +2662,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2753,19 +2709,19 @@
         <v>80</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2774,10 +2730,10 @@
         <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2786,7 +2742,7 @@
         <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2803,10 +2759,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2832,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2888,7 +2844,7 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2897,11 +2853,11 @@
         <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
       </c>
@@ -2909,7 +2865,7 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2926,10 +2882,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2952,16 +2908,16 @@
         <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3011,7 +2967,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -3020,11 +2976,11 @@
         <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
@@ -3032,7 +2988,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -3049,10 +3005,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3075,16 +3031,16 @@
         <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3134,7 +3090,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -3143,11 +3099,11 @@
         <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
       </c>
@@ -3155,7 +3111,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -3172,10 +3128,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3198,16 +3154,16 @@
         <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3257,7 +3213,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3266,11 +3222,11 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
       </c>
@@ -3278,7 +3234,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -3295,10 +3251,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3321,16 +3277,16 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3356,31 +3312,31 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3389,11 +3345,11 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
       </c>
@@ -3401,7 +3357,7 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>80</v>
@@ -3410,7 +3366,7 @@
         <v>80</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>80</v>
@@ -3418,10 +3374,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3444,16 +3400,16 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3479,13 +3435,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3503,7 +3459,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3512,11 +3468,11 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3524,7 +3480,7 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -3533,7 +3489,7 @@
         <v>80</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3541,10 +3497,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3567,16 +3523,16 @@
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3626,7 +3582,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3635,11 +3591,11 @@
         <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3647,7 +3603,7 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -3664,10 +3620,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3690,16 +3646,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3725,13 +3681,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3749,7 +3705,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3758,11 +3714,11 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3770,7 +3726,7 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -3787,14 +3743,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3813,16 +3769,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3872,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3881,11 +3837,11 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3893,7 +3849,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3910,14 +3866,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3936,16 +3892,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3995,7 +3951,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4016,7 +3972,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -4033,14 +3989,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4059,16 +4015,16 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4106,19 +4062,19 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4127,10 +4083,10 @@
         <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -4139,7 +4095,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -4156,10 +4112,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4182,13 +4138,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4227,19 +4183,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4248,10 +4204,10 @@
         <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -4277,10 +4233,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4303,19 +4259,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4364,7 +4320,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4373,39 +4329,39 @@
         <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4428,13 +4384,13 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4485,7 +4441,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4494,39 +4450,39 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4549,16 +4505,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4569,29 +4525,29 @@
         <v>80</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="T21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4608,7 +4564,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>93</v>
@@ -4617,39 +4573,39 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4672,16 +4628,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4707,13 +4663,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4731,7 +4687,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4740,28 +4696,28 @@
         <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4769,10 +4725,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4795,16 +4751,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4830,11 +4786,11 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4852,7 +4808,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4861,43 +4817,43 @@
         <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AK23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4916,16 +4872,16 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4951,11 +4907,11 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4973,7 +4929,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4982,39 +4938,39 @@
         <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5037,17 +4993,15 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5096,7 +5050,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5105,43 +5059,43 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5160,16 +5114,16 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5219,7 +5173,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5228,25 +5182,25 @@
         <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK26" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5257,10 +5211,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5283,16 +5237,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5342,7 +5296,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5351,39 +5305,39 @@
         <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5406,16 +5360,16 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5465,7 +5419,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5474,39 +5428,39 @@
         <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5529,16 +5483,16 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5588,7 +5542,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5597,19 +5551,19 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5626,10 +5580,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5652,16 +5606,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5711,7 +5665,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5720,19 +5674,19 @@
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5744,15 +5698,15 @@
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5775,13 +5729,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5832,7 +5786,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5853,7 +5807,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5870,14 +5824,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5896,16 +5850,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5943,19 +5897,19 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5964,10 +5918,10 @@
         <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5976,7 +5930,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5993,14 +5947,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6019,19 +5973,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -6080,7 +6034,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6089,10 +6043,10 @@
         <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -6101,7 +6055,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -6118,10 +6072,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6144,16 +6098,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6179,13 +6133,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6203,7 +6157,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>93</v>
@@ -6212,19 +6166,19 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -6236,15 +6190,15 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6267,17 +6221,15 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6326,7 +6278,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>93</v>
@@ -6335,19 +6287,19 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6359,15 +6311,15 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6390,19 +6342,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6451,7 +6403,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6460,11 +6412,11 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6472,7 +6424,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6481,18 +6433,18 @@
         <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6515,19 +6467,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6552,14 +6504,14 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y37" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6576,7 +6528,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6585,39 +6537,39 @@
         <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6640,13 +6592,13 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6697,7 +6649,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6706,19 +6658,19 @@
         <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6735,10 +6687,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6761,13 +6713,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6818,7 +6770,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6839,7 +6791,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6856,14 +6808,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6882,16 +6834,16 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6929,19 +6881,19 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6950,10 +6902,10 @@
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6962,7 +6914,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6979,14 +6931,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7005,19 +6957,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7066,7 +7018,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7075,10 +7027,10 @@
         <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7087,7 +7039,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7104,10 +7056,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7130,17 +7082,15 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7189,7 +7139,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7198,39 +7148,39 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7253,13 +7203,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7310,7 +7260,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7331,7 +7281,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7348,14 +7298,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7374,16 +7324,16 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7421,19 +7371,19 @@
         <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC44" t="s" s="2">
+      <c r="AF44" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7442,10 +7392,10 @@
         <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7454,7 +7404,7 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7471,10 +7421,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7497,19 +7447,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7522,7 +7470,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7534,13 +7482,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7558,7 +7506,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7567,11 +7515,11 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7579,7 +7527,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7588,7 +7536,7 @@
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7596,10 +7544,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7622,19 +7570,17 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7647,7 +7593,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7659,13 +7605,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7683,7 +7629,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7692,11 +7638,11 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7704,7 +7650,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7721,10 +7667,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7747,19 +7693,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7808,7 +7754,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7817,11 +7763,11 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7829,7 +7775,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7838,7 +7784,7 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7846,10 +7792,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7872,19 +7818,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7897,7 +7843,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7933,7 +7879,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7942,11 +7888,11 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7954,7 +7900,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7963,7 +7909,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7971,10 +7917,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7997,19 +7943,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8058,7 +8004,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8067,11 +8013,11 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
@@ -8079,7 +8025,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8096,10 +8042,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8122,19 +8068,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8183,7 +8129,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8192,11 +8138,11 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
       </c>
@@ -8204,7 +8150,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8221,10 +8167,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8247,19 +8193,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8272,7 +8216,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8308,7 +8252,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8317,11 +8261,11 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8329,7 +8273,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8346,10 +8290,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8372,17 +8316,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8431,7 +8375,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8440,11 +8384,11 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8452,7 +8396,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8469,10 +8413,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8495,16 +8439,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8530,11 +8474,11 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8552,7 +8496,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8561,39 +8505,39 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8616,16 +8560,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8675,7 +8619,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8684,11 +8628,11 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8696,7 +8640,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8713,10 +8657,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8739,13 +8683,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8796,7 +8740,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8817,7 +8761,7 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8834,14 +8778,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8860,16 +8804,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8907,19 +8851,19 @@
         <v>80</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8928,10 +8872,10 @@
         <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8940,7 +8884,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8957,14 +8901,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8983,19 +8927,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9044,7 +8988,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9053,10 +8997,10 @@
         <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9065,7 +9009,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9082,10 +9026,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9108,17 +9052,15 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9167,7 +9109,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9176,25 +9118,25 @@
         <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK58" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9205,10 +9147,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9231,16 +9173,16 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9266,13 +9208,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9290,7 +9232,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9299,19 +9241,19 @@
         <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9320,18 +9262,18 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9354,17 +9296,15 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9413,7 +9353,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9422,39 +9362,39 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9477,17 +9417,15 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9512,11 +9450,11 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9534,7 +9472,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9543,39 +9481,39 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9598,19 +9536,19 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9635,11 +9573,11 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9657,7 +9595,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9666,39 +9604,39 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9721,17 +9659,15 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9780,7 +9716,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9789,22 +9725,22 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9813,15 +9749,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9844,16 +9780,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9903,7 +9839,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9912,22 +9848,22 @@
         <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9936,7 +9872,7 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T13:26:49+00:00</t>
+    <t>2024-09-23T13:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,7 +441,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -461,7 +461,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1364,7 +1364,7 @@
     <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
   </si>
   <si>
-    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
   </si>
   <si>
     <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T13:29:51+00:00</t>
+    <t>2024-09-24T15:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T15:02:27+00:00</t>
+    <t>2024-09-25T14:04:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/main/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T14:04:17+00:00</t>
+    <t>2024-10-02T09:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
